--- a/ig/main/ValueSet-jdv-j332-type-act-medico-sociale-regulee-finess.xlsx
+++ b/ig/main/ValueSet-jdv-j332-type-act-medico-sociale-regulee-finess.xlsx
@@ -108,7 +108,7 @@
     <t>=</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r374-nature-activite-smsse-regulee#AMSR</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r374-nature-activite-smsse-regulee|AMSR</t>
   </si>
   <si>
     <t/>

--- a/ig/main/ValueSet-jdv-j332-type-act-medico-sociale-regulee-finess.xlsx
+++ b/ig/main/ValueSet-jdv-j332-type-act-medico-sociale-regulee-finess.xlsx
@@ -108,7 +108,7 @@
     <t>=</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r374-nature-activite-smsse-regulee|AMSR</t>
+    <t>AMSR</t>
   </si>
   <si>
     <t/>

--- a/ig/main/ValueSet-jdv-j332-type-act-medico-sociale-regulee-finess.xlsx
+++ b/ig/main/ValueSet-jdv-j332-type-act-medico-sociale-regulee-finess.xlsx
@@ -108,7 +108,7 @@
     <t>=</t>
   </si>
   <si>
-    <t>AMSR</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r374-nature-activite-smsse-regulee#AMSR</t>
   </si>
   <si>
     <t/>
